--- a/.cursor/scratch/tax_turbo_parts/GCM.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/GCM.xlsx
@@ -462,7 +462,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -478,14 +478,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GCM / Gates Capital 2025 — board fees vs reimbursements (not tax advice)</t>
+          <t>GCM / Gates Capital 2025 — personal 1099 (NOT EPGC Consultant) — not tax advice</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BOM PAYMEN $21500.00 = Form 1099-NEC $21,500 → EPGC Consultant + this tab. JAKE C / SEFOF reimbursements $5214.69 EXCLUDED. CPA: confirm EPGC LLC vs personal 1099/Sch C.</t>
+          <t>BOM PAYMEN $21500.00 = Form 1099-NEC $21,500 → this tab + Income E7 only. User 2026-09-18: remove GCM from the EPGC Consultant line (1099 is in Jacob’s name). JAKE C / SEFOF reimbursements $5214.69 EXCLUDED (May 22 $609.02 CONFIRMED reimbursement).</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Board fee (BOM PAYMEN → Consultant)</t>
+          <t>Board fee (BOM PAYMEN → personal 1099 / GCM tab)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -712,7 +712,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Consultant / 1099</t>
+          <t>Personal 1099 / GCM tab</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — not EPGC Consultant</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Consultant / 1099</t>
+          <t>Personal 1099 / GCM tab</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — not EPGC Consultant</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Consultant / 1099</t>
+          <t>Personal 1099 / GCM tab</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — not EPGC Consultant</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Consultant / 1099</t>
+          <t>Personal 1099 / GCM tab</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — not EPGC Consultant</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>JAKE C — no PMT INFO on statement; odd cents, not BOM — treated as reimburse</t>
+          <t>CONFIRMED reimbursement (JAKE C, not BOM)</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>SEFOF WHARTON EXPENSES — not on the two BoA folders</t>
+          <t>SEFOF WHARTON EXPENSES — WAIT 8507 statements</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>SEFOF ANNUAL CONFERENCE EXPENSES</t>
+          <t>SEFOF ANNUAL CONFERENCE EXPENSES — WAIT 8507 statements</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>SEFOF REIMBURSE EXPENSES FOR EDUCATION COMMITTEE</t>
+          <t>SEFOF EDUCATION COMMITTEE — WAIT 8507 statements</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>1099-NEC Gates Capital Management LLC TIN 84-1331261 box 1 = $21,500. BOM sum ties. Reimbursements are not on the 1099.</t>
+          <t>1099-NEC Gates Capital Management LLC TIN 84-1331261 box 1 = $21,500. BOM sum ties. Reimbursements are not on the 1099. EPGC Consultant is $0.</t>
         </is>
       </c>
     </row>
